--- a/artfynd/A 24959-2025 artfynd.xlsx
+++ b/artfynd/A 24959-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017194</v>
       </c>
       <c r="B2" t="n">
-        <v>79557</v>
+        <v>79561</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24959-2025 artfynd.xlsx
+++ b/artfynd/A 24959-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017194</v>
       </c>
       <c r="B2" t="n">
-        <v>79561</v>
+        <v>79562</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24959-2025 artfynd.xlsx
+++ b/artfynd/A 24959-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017194</v>
       </c>
       <c r="B2" t="n">
-        <v>79562</v>
+        <v>79566</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24959-2025 artfynd.xlsx
+++ b/artfynd/A 24959-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017194</v>
       </c>
       <c r="B2" t="n">
-        <v>79566</v>
+        <v>79569</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
